--- a/dolbomon_resources.xlsx
+++ b/dolbomon_resources.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="166">
   <si>
     <t>표시명</t>
   </si>
@@ -119,10 +119,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>체조</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>건강100세운동교실</t>
   </si>
   <si>
@@ -143,10 +139,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>건강검진</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>프로그램명</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -159,6 +151,3143 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
+      <t>건강검진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사후관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대사증후군</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~3</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>건강생활실천금지원금제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시범사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~5</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>국가건강검진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1~3</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>금연치료 지원사업</t>
+  </si>
+  <si>
+    <t>대사증후군,건강검진 사후관리</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>금연치료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지원사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1~6</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>낙상예방 재가환경지원 시범사업</t>
+  </si>
+  <si>
+    <t>요양</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>낙상예방</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재가환경지원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시범사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~2</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>노인건강 마일리지사업</t>
+  </si>
+  <si>
+    <t>건강관리</t>
+  </si>
+  <si>
+    <t>노인건강,마일리지</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노인건강마일리지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1~3</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>다제약물 관리사업</t>
+  </si>
+  <si>
+    <t>방문복약관리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다제약물관리사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~3</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만성질환건강지원사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~3</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>만성질환 건강지원사업</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>복지용구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1~3</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>복지용구</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>요양</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>복지용구</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>사전연명의료의향서 작성(상담/등록)</t>
+  </si>
+  <si>
+    <t>사전연명의료의향서 작성1~4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요양병원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>간병지원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시범사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~2</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>요양병원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>간병지원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시범사업</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요양병원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>퇴원환자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지원제도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~6</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요양병원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>퇴원환자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지원제도</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>보건의료</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">요양병원 퇴원환자지원제도 </t>
+  </si>
+  <si>
+    <r>
+      <t>요양병원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>호스피스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건강보험수가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시범사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~4</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>요양병원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>호스피스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건강보험수가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시범사업</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>호스피스</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요양비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>급여비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당뇨병환자소모성재료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~3</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요양비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>급여비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당뇨병환자소모성재료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요양비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당뇨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소모성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일차의료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만성질환관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~3</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일차의료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만성질환관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사업</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>일차의료 만성질환관리 사업</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장기요양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가족휴가제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1~2</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>요양</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>방문요양</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장기요양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가족휴가제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방문요양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>장기요양 가족휴가제(방문요양)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장기요양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가족휴가제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단기보호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>장기요양 가족휴가제(단기보호)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>단기보호</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장기요양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>병원동행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시범사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>병원동행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동행</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>장기요양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재택의료센터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시범사업</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>보건의료</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>방문진료</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>재택의료</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장기요양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재택의료센터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시범사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~5</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합재가</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>요양</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타</t>
+  </si>
+  <si>
+    <t>기타</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합재가서비스</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장기요양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통합재가서비스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~3</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장애인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건강주치의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시범사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~3</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>건강관리예방</t>
+  </si>
+  <si>
+    <t>장애인 건강관리</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>장애인 건강주치의 시범사업</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건강주치의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주치의</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장애인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>치과주치의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시범사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~2</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>장애인 치과주치의 시범사업</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>치과주치의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주치의</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>장애인 건강관리</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>장애인보조기기 급여비</t>
+  </si>
+  <si>
+    <t>장애인보조기기 급여비1~5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>보조기기</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>장애인의료비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지원사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~4</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>장애인의료비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지원사업</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>의료비</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>재난적의료비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지원사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~4</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>재난적의료비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지원사업</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>재난적의료비 지원사업</t>
+  </si>
+  <si>
+    <t>기타</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>정신건강관리</t>
+  </si>
+  <si>
+    <t>정신건강 심리상담 바우처사업</t>
+  </si>
+  <si>
+    <t>정신건강 심리상담 바우처사업1~5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정신건강</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>심리상담</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바우처</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바우쳐</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>단기보호</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>주야간 보호기관 내 단기보호 시범사업</t>
+  </si>
+  <si>
+    <t>주야간 보호기관 내 단기보호 시범사업1~4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>단기보호</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>치과시술 등록제1~3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>치과시술</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등록제</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>치과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>치과시술등록제</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>치매전문관리</t>
+  </si>
+  <si>
+    <t>치매치료관리비 지원사업</t>
+  </si>
+  <si>
+    <r>
+      <t>치매치료관리비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지원사업</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>치매치료,관리비</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>치매치료관리비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지원사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~4</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장기요양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재가급여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이용안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1~6</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>방문요양</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>방문목욕</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>방문간호</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>주야간보호</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>단기보호</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방문요양</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목욕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방문목욕</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>간호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방문간호</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주야간보호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주간보호</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>요양</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>방문목욕</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>방문간호</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>주야간보호</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>단기보호</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>금연</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>담배</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흡연</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>체조,경로당</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>낙상,집수리,집 수리,수리</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>건강검진,위,대장,검사</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지팡이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목욕의자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안전손잡이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전동침대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수동침대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배회감지기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보행기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요실금팬티</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>혈압기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>혈당기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고혈압</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당뇨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건강상담</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건강문고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>집중상담</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자조모임</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장기요양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가족휴가제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방문요양</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>임종</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>치료중단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>치료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>심폐소생술</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>재택의료,의사,간호사,방문진료,가정진료,집,자택,왕진</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>치매,1등급,2등급,1~2등급,종일</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>간병지원,간병비</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>급성기</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>당뇨병,소모성,소모성재료,급여비,출산,혈당측정,채혈침,인슐린,주사,바늘,자가투약</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>만성질환관리,병의원,혈압,고혈압,당뇨</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장기요양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>병원동행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시범사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
       <t>건강</t>
     </r>
     <r>
@@ -166,6 +3295,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>100</t>
     </r>
@@ -184,166 +3314,26 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~5</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>건강검진</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사후관리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대사증후군</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>)1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~3</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>건강생활실천금지원금제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시범사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~5</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>국가건강검진</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1~3</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>금연치료 지원사업</t>
-  </si>
-  <si>
-    <t>대사증후군,건강검진 사후관리</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>금연</t>
+        <family val="2"/>
+      </rPr>
+      <t>1~2</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합재가,방문요양,방문간호,주간보호,주야간보호</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다제</t>
     </r>
     <r>
       <rPr>
@@ -362,7 +3352,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>담배</t>
+      <t>다제약물</t>
     </r>
     <r>
       <rPr>
@@ -381,194 +3371,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>흡연</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>금연치료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지원사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1~6</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>낙상예방 재가환경지원 시범사업</t>
-  </si>
-  <si>
-    <t>낙상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>요양</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>기타</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>낙상예방</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>재가환경지원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시범사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>노인건강 마일리지사업</t>
-  </si>
-  <si>
-    <t>건강관리</t>
-  </si>
-  <si>
-    <t>노인건강,마일리지</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>노인건강마일리지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1~3</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>다제약물 관리사업</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>다제</t>
+      <t>약사</t>
     </r>
     <r>
       <rPr>
@@ -587,86 +3390,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>다제약물</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>방문복약관리</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>다제약물관리사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~3</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>만성질환건강지원사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~3</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>만성질환 건강지원사업</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>만성질환</t>
+      <t>남용</t>
     </r>
     <r>
       <rPr>
@@ -685,7 +3409,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>건강지원</t>
+      <t>복약</t>
     </r>
     <r>
       <rPr>
@@ -704,2492 +3428,8 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>혈압기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>복지용구</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1~3</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>복지용구</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>복지용구</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지팡이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>목욕의자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>안전손잡이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>전동침대</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수동침대</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>배회감지기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보행기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>요실금팬티</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>요양</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>복지용구</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>사전연명의료의향서 작성(상담/등록)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사전</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사전연명</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>사전연명의료의향서 작성1~4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>요양병원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>간병지원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시범사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>요양병원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>간병지원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시범사업</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>간병지원</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>요양병원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>퇴원환자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지원제도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~6</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>요양병원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>퇴원환자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지원제도</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>퇴원환자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>보건의료</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>기타</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">요양병원 퇴원환자지원제도 </t>
-  </si>
-  <si>
-    <r>
-      <t>요양병원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>호스피스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>건강보험수가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시범사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~4</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>요양병원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>호스피스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>건강보험수가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시범사업</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>호스피스</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>요양비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>급여비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>당뇨병환자소모성재료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>)1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~3</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>요양비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>급여비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>당뇨병환자소모성재료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>요양비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지급</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>당뇨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>소모성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>재료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>당뇨병,소모성,소모성재료,급여비</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>일차의료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>만성질환관리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~3</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>일차의료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>만성질환관리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사업</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>만성질환관리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>일차의료</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>일차의료 만성질환관리 사업</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장기요양</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가족휴가제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1~2</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>요양</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>방문요양</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장기요양</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가족휴가제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>방문요양</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>장기요양 가족휴가제(방문요양)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장기요양</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가족휴가제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>단기보호</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장기요양</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가족휴가제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>방문요양</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>장기요양 가족휴가제(단기보호)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>단기보호</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장기요양</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>병원동행</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시범사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~6</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장기요양</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>병원동행</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시범사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>병원동행</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>동행</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>장기요양</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>재택의료센터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시범사업</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>보건의료</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>방문진료</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>재택의료</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>재택의료</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장기요양</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>재택의료센터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시범사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~5</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>통합재가</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>요양</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>기타</t>
-  </si>
-  <si>
-    <t>기타</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>통합재가서비스</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장기요양</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>통합재가서비스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~3</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장애인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>건강주치의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시범사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~3</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>건강관리예방</t>
-  </si>
-  <si>
-    <t>장애인 건강관리</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>장애인 건강주치의 시범사업</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>건강주치의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주치의</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장애인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>치과주치의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시범사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~2</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>장애인 치과주치의 시범사업</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>치과주치의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주치의</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>장애인 건강관리</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>장애인보조기기 급여비</t>
-  </si>
-  <si>
-    <t>장애인보조기기 급여비1~5</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>보조기기</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>장애인의료비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지원사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~4</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>장애인의료비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지원사업</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>의료비</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>재난적의료비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지원사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~4</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>재난적의료비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지원사업</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>재난적의료비 지원사업</t>
-  </si>
-  <si>
-    <t>기타</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>정신건강관리</t>
-  </si>
-  <si>
-    <t>정신건강 심리상담 바우처사업</t>
-  </si>
-  <si>
-    <t>정신건강 심리상담 바우처사업1~5</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>재난적,의료비</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정신건강</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>심리상담</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바우처</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바우쳐</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>단기보호</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>주야간 보호기관 내 단기보호 시범사업</t>
-  </si>
-  <si>
-    <t>주야간 보호기관 내 단기보호 시범사업1~4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>단기보호</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>치과시술 등록제1~3</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>치과시술</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등록제</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>치과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>치과시술등록제</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>치매전문관리</t>
-  </si>
-  <si>
-    <t>치매치료관리비 지원사업</t>
-  </si>
-  <si>
-    <r>
-      <t>치매치료관리비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지원사업</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>치매치료,관리비</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>치매치료관리비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지원사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~4</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장기요양</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>재가급여</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이용안내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1~6</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>방문요양</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>방문목욕</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>방문간호</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>주야간보호</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>단기보호</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>요양</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>방문요양</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>목욕</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>방문목욕</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>간호</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>방문간호</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주야간보호</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주간보호</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>단기보호</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>요양</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>방문목욕</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>방문간호</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>주야간보호</t>
+      <t>비순응</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -3214,15 +3454,18 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -3253,7 +3496,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3263,6 +3506,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B7EE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3304,7 +3553,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3348,6 +3597,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3653,12 +3915,12 @@
   <dimension ref="A1:G291"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="28.69921875" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32" style="15" customWidth="1"/>
+    <col min="1" max="1" width="32.8984375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="59.3984375" style="15" customWidth="1"/>
     <col min="3" max="3" width="14" style="15" customWidth="1"/>
     <col min="4" max="4" width="16" style="15" customWidth="1"/>
     <col min="5" max="5" width="28.69921875" style="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="75.09765625" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.69921875" style="16" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3676,7 +3938,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>5</v>
@@ -3690,7 +3952,7 @@
         <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>18</v>
@@ -3699,21 +3961,21 @@
         <v>19</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>30</v>
+        <v>21</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>162</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>18</v>
@@ -3722,21 +3984,21 @@
         <v>19</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>24</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>25</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>18</v>
@@ -3745,21 +4007,21 @@
         <v>19</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>18</v>
@@ -3768,21 +4030,21 @@
         <v>19</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>36</v>
+        <v>31</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>147</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>18</v>
@@ -3791,245 +4053,243 @@
         <v>19</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>164</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>53</v>
+        <v>46</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>152</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>60</v>
+        <v>51</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>154</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A13" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>63</v>
+      <c r="B13" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>74</v>
+        <v>158</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>80</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B15" s="9"/>
       <c r="C15" s="9" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>84</v>
+        <v>159</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>87</v>
+        <v>74</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>160</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>18</v>
@@ -4038,444 +4298,442 @@
         <v>19</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>95</v>
+        <v>79</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>156</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>95</v>
+        <v>81</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>153</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="10" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
-      <c r="F20" s="10" t="s">
-        <v>98</v>
+      <c r="F20" s="14" t="s">
+        <v>161</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="9" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>105</v>
+        <v>155</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="9" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="5" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="5" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="5" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="9" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>135</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="B27" s="5"/>
       <c r="C27" s="9" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="5" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="5" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="9" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="9" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="9" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>156</v>
+        <v>134</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>139</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" s="9" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="9" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="9" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
@@ -6775,7 +7033,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" sqref="G2:G291">
       <formula1>"Y,N"</formula1>
     </dataValidation>
